--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W774"/>
+  <dimension ref="A1:W775"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35253,6 +35253,58 @@
         <v>10</v>
       </c>
     </row>
+    <row r="775">
+      <c r="A775" s="2">
+        <v>46278</v>
+      </c>
+      <c r="B775" s="2">
+        <v>46269</v>
+      </c>
+      <c r="C775" s="2">
+        <v>46274</v>
+      </c>
+      <c r="D775" s="2">
+        <v>46271</v>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Red C</t>
+        </is>
+      </c>
+      <c r="F775">
+        <v>1010</v>
+      </c>
+      <c r="G775">
+        <v>14</v>
+      </c>
+      <c r="H775">
+        <v>18</v>
+      </c>
+      <c r="I775">
+        <v>21</v>
+      </c>
+      <c r="J775">
+        <v>4</v>
+      </c>
+      <c r="K775">
+        <v>3</v>
+      </c>
+      <c r="O775">
+        <v>3</v>
+      </c>
+      <c r="Q775">
+        <v>11</v>
+      </c>
+      <c r="R775">
+        <v>7</v>
+      </c>
+      <c r="S775">
+        <v>5</v>
+      </c>
+      <c r="W775">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_polls.xlsx
+++ b/data_polls.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W775"/>
+  <dimension ref="A1:W776"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35305,6 +35305,58 @@
         <v>14</v>
       </c>
     </row>
+    <row r="776">
+      <c r="A776" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B776" s="2">
+        <v>46286</v>
+      </c>
+      <c r="C776" s="2">
+        <v>46287</v>
+      </c>
+      <c r="D776" s="2">
+        <v>46286</v>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Ipsos B&amp;A</t>
+        </is>
+      </c>
+      <c r="F776">
+        <v>1200</v>
+      </c>
+      <c r="G776">
+        <v>18</v>
+      </c>
+      <c r="H776">
+        <v>17</v>
+      </c>
+      <c r="I776">
+        <v>23</v>
+      </c>
+      <c r="J776">
+        <v>4</v>
+      </c>
+      <c r="K776">
+        <v>3</v>
+      </c>
+      <c r="O776">
+        <v>3</v>
+      </c>
+      <c r="Q776">
+        <v>8</v>
+      </c>
+      <c r="R776">
+        <v>5</v>
+      </c>
+      <c r="S776">
+        <v>4</v>
+      </c>
+      <c r="W776">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
